--- a/Dataset_combinato_GPS_finale.xlsx
+++ b/Dataset_combinato_GPS_finale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riki/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E49643E-9A6C-0F4A-9080-FC0608999DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85C4AC7-76E6-944E-BF62-2F8772833F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,6 +299,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="m/d/yy;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -354,7 +357,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Dataset_combinato_GPS_finale.xlsx
+++ b/Dataset_combinato_GPS_finale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riki/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85C4AC7-76E6-944E-BF62-2F8772833F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B060FBB6-8D6E-B74E-8F3D-6A1194A4E320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,9 +299,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="m/d/yy;@"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -352,12 +349,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -662,9 +662,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11" style="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -732,7 +735,7 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>45725</v>
       </c>
       <c r="B2" t="s">
@@ -800,7 +803,7 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>45725</v>
       </c>
       <c r="B3" t="s">
@@ -868,7 +871,7 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>45725</v>
       </c>
       <c r="B4" t="s">
@@ -936,7 +939,7 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>45725</v>
       </c>
       <c r="B5" t="s">
@@ -1004,7 +1007,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>45725</v>
       </c>
       <c r="B6" t="s">
@@ -1072,7 +1075,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>45725</v>
       </c>
       <c r="B7" t="s">
@@ -1140,7 +1143,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>45725</v>
       </c>
       <c r="B8" t="s">
@@ -1208,7 +1211,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>45725</v>
       </c>
       <c r="B9" t="s">
@@ -1276,7 +1279,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>45725</v>
       </c>
       <c r="B10" t="s">
@@ -1344,7 +1347,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45725</v>
       </c>
       <c r="B11" t="s">
@@ -1412,7 +1415,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45725</v>
       </c>
       <c r="B12" t="s">
@@ -1480,7 +1483,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45756</v>
       </c>
       <c r="B13" t="s">
@@ -1548,7 +1551,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45756</v>
       </c>
       <c r="B14" t="s">
@@ -1616,7 +1619,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45756</v>
       </c>
       <c r="B15" t="s">
@@ -1684,7 +1687,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45756</v>
       </c>
       <c r="B16" t="s">
@@ -1752,7 +1755,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45756</v>
       </c>
       <c r="B17" t="s">
@@ -1820,7 +1823,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45756</v>
       </c>
       <c r="B18" t="s">
@@ -1888,7 +1891,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45756</v>
       </c>
       <c r="B19" t="s">
@@ -1956,7 +1959,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45756</v>
       </c>
       <c r="B20" t="s">
@@ -2024,7 +2027,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45786</v>
       </c>
       <c r="B21" t="s">
@@ -2092,7 +2095,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45786</v>
       </c>
       <c r="B22" t="s">
@@ -2160,7 +2163,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45786</v>
       </c>
       <c r="B23" t="s">
@@ -2228,7 +2231,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45786</v>
       </c>
       <c r="B24" t="s">
@@ -2296,7 +2299,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45786</v>
       </c>
       <c r="B25" t="s">
@@ -2364,7 +2367,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45786</v>
       </c>
       <c r="B26" t="s">
@@ -2432,7 +2435,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45786</v>
       </c>
       <c r="B27" t="s">
@@ -2500,7 +2503,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45786</v>
       </c>
       <c r="B28" t="s">
@@ -2568,7 +2571,7 @@
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>45786</v>
       </c>
       <c r="B29" t="s">
@@ -2636,7 +2639,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>45786</v>
       </c>
       <c r="B30" t="s">
@@ -2704,7 +2707,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>45817</v>
       </c>
       <c r="B31" t="s">
@@ -2772,7 +2775,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>45817</v>
       </c>
       <c r="B32" t="s">
@@ -2840,7 +2843,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>45817</v>
       </c>
       <c r="B33" t="s">
@@ -2908,7 +2911,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>45817</v>
       </c>
       <c r="B34" t="s">
@@ -2976,7 +2979,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>45817</v>
       </c>
       <c r="B35" t="s">
@@ -3044,7 +3047,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>45817</v>
       </c>
       <c r="B36" t="s">
@@ -3112,7 +3115,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>45817</v>
       </c>
       <c r="B37" t="s">
@@ -3180,7 +3183,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>45817</v>
       </c>
       <c r="B38" t="s">
@@ -3248,7 +3251,7 @@
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>45817</v>
       </c>
       <c r="B39" t="s">
@@ -3316,7 +3319,7 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>45817</v>
       </c>
       <c r="B40" t="s">
@@ -3384,7 +3387,7 @@
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>45817</v>
       </c>
       <c r="B41" t="s">

--- a/Dataset_combinato_GPS_finale.xlsx
+++ b/Dataset_combinato_GPS_finale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riki/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B060FBB6-8D6E-B74E-8F3D-6A1194A4E320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7156195-FDE4-E841-B921-81A4D119C114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4460" yWindow="3540" windowWidth="34560" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -299,6 +299,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -354,10 +357,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,7 +666,7 @@
   <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
